--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="290">
   <si>
     <t/>
   </si>
   <si>
-    <t>20143040</t>
-  </si>
-  <si>
-    <t>OBLB SQR ORI FLV CKE</t>
+    <t>20065216</t>
+  </si>
+  <si>
+    <t>SHARON CK STM BANANA</t>
   </si>
   <si>
     <t>BAK02D</t>
@@ -31,126 +31,120 @@
     <t>RT,(E-1H)</t>
   </si>
   <si>
-    <t>20143042</t>
-  </si>
-  <si>
-    <t>OBLB TRGLE CHO CAKE</t>
+    <t>20056133</t>
+  </si>
+  <si>
+    <t>SHARON STMED CHEESE</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20143043</t>
-  </si>
-  <si>
-    <t>OBLB TRGLE CHSE CAKE</t>
+    <t>20062276</t>
+  </si>
+  <si>
+    <t>SHARON CK STMED CKLT</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20143041</t>
-  </si>
-  <si>
-    <t>OBLB TRNGLE STRW CKE</t>
+    <t>20036033</t>
+  </si>
+  <si>
+    <t>SHARON CREAM MESS40</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20142878</t>
-  </si>
-  <si>
-    <t>DALEZZ MUFFIN 84G</t>
+    <t>20017738</t>
+  </si>
+  <si>
+    <t>SHARON RT.SISIR MTGA</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10013738</t>
+  </si>
+  <si>
+    <t>SHRON CRM MESSES 200</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20042687</t>
+  </si>
+  <si>
+    <t>PIE SUSU PCS</t>
+  </si>
+  <si>
+    <t>20111591</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSANT CHOC</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20111592</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSNT BRIES</t>
+  </si>
+  <si>
+    <t>20115438</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSANT CHSE</t>
+  </si>
+  <si>
+    <t>20125077</t>
+  </si>
+  <si>
+    <t>5DAYS CRSNT PD SKY60</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>20136661</t>
+  </si>
+  <si>
+    <t>5 DAYS CHOCO BANANA</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20143387</t>
+  </si>
+  <si>
+    <t>5DAYS MN CROI STR128</t>
+  </si>
+  <si>
+    <t>20121350</t>
+  </si>
+  <si>
+    <t>5DAYS MN CROIS CHO8S</t>
+  </si>
+  <si>
+    <t>20138569</t>
+  </si>
+  <si>
+    <t>MOOOCHII CHOCO 40G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20142877</t>
-  </si>
-  <si>
-    <t>DALEZZ CUSTARD 100G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20142876</t>
-  </si>
-  <si>
-    <t>DLEZZ SWS.ROL STR 72</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20042687</t>
-  </si>
-  <si>
-    <t>PIE SUSU PCS</t>
-  </si>
-  <si>
-    <t>20111591</t>
-  </si>
-  <si>
-    <t>5DAYS CROISSANT CHOC</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20111592</t>
-  </si>
-  <si>
-    <t>5DAYS CROISSNT BRIES</t>
-  </si>
-  <si>
-    <t>20115438</t>
-  </si>
-  <si>
-    <t>5DAYS CROISSANT CHSE</t>
-  </si>
-  <si>
-    <t>20125077</t>
-  </si>
-  <si>
-    <t>5DAYS CRSNT PD SKY60</t>
-  </si>
-  <si>
-    <t>20136661</t>
-  </si>
-  <si>
-    <t>5 DAYS CHOCO BANANA</t>
-  </si>
-  <si>
-    <t>20143387</t>
-  </si>
-  <si>
-    <t>5DAYS MN CROI STR128</t>
-  </si>
-  <si>
-    <t>20121350</t>
-  </si>
-  <si>
-    <t>5DAYS MN CROIS CHO8S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20138569</t>
-  </si>
-  <si>
-    <t>MOOOCHII CHOCO 40G</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20138567</t>
   </si>
   <si>
@@ -559,169 +553,121 @@
     <t>S/R WAFFLE CHOCO 35G</t>
   </si>
   <si>
-    <t>20065216</t>
-  </si>
-  <si>
-    <t>SHARON CK STM BANANA</t>
-  </si>
-  <si>
-    <t>20056133</t>
-  </si>
-  <si>
-    <t>SHARON STMED CHEESE</t>
-  </si>
-  <si>
-    <t>20062276</t>
-  </si>
-  <si>
-    <t>SHARON CK STMED CKLT</t>
-  </si>
-  <si>
-    <t>20036033</t>
-  </si>
-  <si>
-    <t>SHARON CREAM MESS40</t>
-  </si>
-  <si>
-    <t>20131716</t>
-  </si>
-  <si>
-    <t>SHARON CRM PNUT 40G</t>
-  </si>
-  <si>
-    <t>20064117</t>
-  </si>
-  <si>
-    <t>SHARON DORA YAKI CHO</t>
+    <t>20099290</t>
+  </si>
+  <si>
+    <t>ARNON CHOCO ROLL</t>
+  </si>
+  <si>
+    <t>20054693</t>
+  </si>
+  <si>
+    <t>ARNON ROTI SSR MNTGA</t>
+  </si>
+  <si>
+    <t>20132973</t>
+  </si>
+  <si>
+    <t>ARNON ROTI SSR KEJU</t>
+  </si>
+  <si>
+    <t>20054691</t>
+  </si>
+  <si>
+    <t>ARNON ROTI MESES 5'S</t>
+  </si>
+  <si>
+    <t>20057573</t>
+  </si>
+  <si>
+    <t>ARNON RTI CRM MSS 40</t>
+  </si>
+  <si>
+    <t>20132974</t>
+  </si>
+  <si>
+    <t>ARNON STEAM CHS CAKE</t>
+  </si>
+  <si>
+    <t>20067468</t>
+  </si>
+  <si>
+    <t>ARNON ROTI PSNG CKLT</t>
+  </si>
+  <si>
+    <t>20137768</t>
+  </si>
+  <si>
+    <t>ARNON STEAM CAKE BAN</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>20127597</t>
+  </si>
+  <si>
+    <t>MR.BRD SNDW MRGRN</t>
+  </si>
+  <si>
+    <t>20134627</t>
+  </si>
+  <si>
+    <t>MR.BRD RT ISI DG AYM</t>
+  </si>
+  <si>
+    <t>20138653</t>
+  </si>
+  <si>
+    <t>MR.BREAD MUNG BEAN</t>
+  </si>
+  <si>
+    <t>20136705</t>
+  </si>
+  <si>
+    <t>MR.BREAD SOFT CHOCO</t>
+  </si>
+  <si>
+    <t>20127047</t>
+  </si>
+  <si>
+    <t>MR.BRD SBK SOFT CHSE</t>
+  </si>
+  <si>
+    <t>20129486</t>
+  </si>
+  <si>
+    <t>MR.BRD ISI KEJU SUSU</t>
+  </si>
+  <si>
+    <t>20137419</t>
+  </si>
+  <si>
+    <t>MR.BREAD CKLT KCNG</t>
+  </si>
+  <si>
+    <t>20069665</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR CKLT KEJU</t>
+  </si>
+  <si>
+    <t>20070168</t>
+  </si>
+  <si>
+    <t>MR.BREAD KSR CKLT SS</t>
+  </si>
+  <si>
+    <t>20104117</t>
+  </si>
+  <si>
+    <t>MR.BRD SISIR COKELAT</t>
   </si>
   <si>
     <t>RT</t>
-  </si>
-  <si>
-    <t>20017738</t>
-  </si>
-  <si>
-    <t>SHARON RT.SISIR MTGA</t>
-  </si>
-  <si>
-    <t>10013738</t>
-  </si>
-  <si>
-    <t>SHRON CRM MESSES 200</t>
-  </si>
-  <si>
-    <t>20057573</t>
-  </si>
-  <si>
-    <t>ARNON RTI CRM MSS 40</t>
-  </si>
-  <si>
-    <t>20132974</t>
-  </si>
-  <si>
-    <t>ARNON STEAM CHS CAKE</t>
-  </si>
-  <si>
-    <t>20067468</t>
-  </si>
-  <si>
-    <t>ARNON ROTI PSNG CKLT</t>
-  </si>
-  <si>
-    <t>20137768</t>
-  </si>
-  <si>
-    <t>ARNON STEAM CAKE BAN</t>
-  </si>
-  <si>
-    <t>20099290</t>
-  </si>
-  <si>
-    <t>ARNON CHOCO ROLL</t>
-  </si>
-  <si>
-    <t>20054693</t>
-  </si>
-  <si>
-    <t>ARNON ROTI SSR MNTGA</t>
-  </si>
-  <si>
-    <t>20132973</t>
-  </si>
-  <si>
-    <t>ARNON ROTI SSR KEJU</t>
-  </si>
-  <si>
-    <t>20054691</t>
-  </si>
-  <si>
-    <t>ARNON ROTI MESES 5'S</t>
-  </si>
-  <si>
-    <t>10029542</t>
-  </si>
-  <si>
-    <t>MR.BREAD COKLAT KEJU</t>
-  </si>
-  <si>
-    <t>20127597</t>
-  </si>
-  <si>
-    <t>MR.BRD SNDW MRGRN</t>
-  </si>
-  <si>
-    <t>20134627</t>
-  </si>
-  <si>
-    <t>MR.BRD RT ISI DG AYM</t>
-  </si>
-  <si>
-    <t>20138653</t>
-  </si>
-  <si>
-    <t>MR.BREAD MUNG BEAN</t>
-  </si>
-  <si>
-    <t>20136705</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT CHOCO</t>
-  </si>
-  <si>
-    <t>20127047</t>
-  </si>
-  <si>
-    <t>MR.BRD SBK SOFT CHSE</t>
-  </si>
-  <si>
-    <t>20129486</t>
-  </si>
-  <si>
-    <t>MR.BRD ISI KEJU SUSU</t>
-  </si>
-  <si>
-    <t>20137419</t>
-  </si>
-  <si>
-    <t>MR.BREAD CKLT KCNG</t>
-  </si>
-  <si>
-    <t>20069665</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR CKLT KEJU</t>
-  </si>
-  <si>
-    <t>20070168</t>
-  </si>
-  <si>
-    <t>MR.BREAD KSR CKLT SS</t>
-  </si>
-  <si>
-    <t>20104117</t>
-  </si>
-  <si>
-    <t>MR.BRD SISIR COKELAT</t>
   </si>
   <si>
     <t>20096536</t>
@@ -1327,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1455,15 +1401,15 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1472,38 +1418,38 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1512,18 +1458,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1532,18 +1478,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1552,18 +1498,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1572,18 +1518,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1592,10 +1538,10 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1612,10 +1558,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1632,10 +1578,10 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1655,15 +1601,15 @@
         <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1672,18 +1618,18 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1692,18 +1638,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1712,27 +1658,27 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1752,7 +1698,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1772,7 +1718,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1792,7 +1738,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1812,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1832,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1852,7 +1798,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1869,10 +1815,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1892,7 +1838,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1912,7 +1858,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1932,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1952,7 +1898,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1972,7 +1918,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1992,7 +1938,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2012,7 +1958,7 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2029,10 +1975,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2049,10 +1995,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2069,10 +2015,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2089,10 +2035,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2109,10 +2055,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2129,10 +2075,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2149,10 +2095,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2169,10 +2115,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2189,10 +2135,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2209,10 +2155,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2229,10 +2175,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2249,10 +2195,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2269,10 +2215,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2289,10 +2235,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2309,10 +2255,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2329,7 +2275,7 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>42</v>
@@ -2349,10 +2295,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2369,10 +2315,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2389,10 +2335,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2409,10 +2355,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2420,19 +2366,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2440,19 +2386,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2460,19 +2406,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2489,7 +2435,7 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>4</v>
@@ -2509,7 +2455,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>4</v>
@@ -2529,10 +2475,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2549,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
@@ -2569,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>8</v>
@@ -2589,10 +2535,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2609,7 +2555,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>11</v>
@@ -2629,7 +2575,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>11</v>
@@ -2649,10 +2595,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2669,7 +2615,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>14</v>
@@ -2689,7 +2635,7 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>14</v>
@@ -2709,10 +2655,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2729,10 +2675,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2749,10 +2695,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2769,10 +2715,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2789,10 +2735,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2809,10 +2755,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2829,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2849,10 +2795,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2869,10 +2815,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2889,10 +2835,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2909,10 +2855,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2929,10 +2875,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2949,7 +2895,7 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>42</v>
@@ -2969,10 +2915,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2989,10 +2935,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3009,10 +2955,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3029,10 +2975,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3052,7 +2998,7 @@
         <v>42</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3072,7 +3018,7 @@
         <v>42</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3092,18 +3038,18 @@
         <v>42</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3112,7 +3058,7 @@
         <v>42</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3120,19 +3066,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3140,19 +3086,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3160,19 +3106,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3180,19 +3126,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3200,19 +3146,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3220,19 +3166,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3240,19 +3186,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3260,19 +3206,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3280,19 +3226,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3300,19 +3246,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3320,22 +3266,22 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3349,10 +3295,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3369,10 +3315,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3389,10 +3335,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3409,10 +3355,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3429,10 +3375,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3449,10 +3395,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3469,10 +3415,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3489,10 +3435,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3509,13 +3455,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3529,10 +3475,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3549,7 +3495,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>17</v>
@@ -3569,10 +3515,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3589,10 +3535,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3609,10 +3555,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3629,10 +3575,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3649,10 +3595,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3669,10 +3615,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3689,10 +3635,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3709,10 +3655,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3729,10 +3675,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3749,10 +3695,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3769,10 +3715,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3789,10 +3735,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3809,10 +3755,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3829,10 +3775,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3849,10 +3795,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3869,10 +3815,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3889,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>24</v>
+        <v>275</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3900,19 +3846,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>278</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3920,282 +3866,102 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>128</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>128</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>128</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>128</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="283">
   <si>
     <t/>
   </si>
@@ -385,409 +385,388 @@
     <t>13</t>
   </si>
   <si>
-    <t>20137879</t>
-  </si>
-  <si>
-    <t>SARI KUE VAN.C 6'S</t>
+    <t>20036000</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND K/KCG</t>
+  </si>
+  <si>
+    <t>20072596</t>
+  </si>
+  <si>
+    <t>SARI ROTI LAPIS BMKH</t>
+  </si>
+  <si>
+    <t>20127599</t>
+  </si>
+  <si>
+    <t>S/R LPIS SRBY ORI 48</t>
+  </si>
+  <si>
+    <t>20046107</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND BLUBR</t>
+  </si>
+  <si>
+    <t>20080782</t>
+  </si>
+  <si>
+    <t>SR LAPIS BMKHN CKLAT</t>
+  </si>
+  <si>
+    <t>20132616</t>
+  </si>
+  <si>
+    <t>S/ROTI ZPR SNDW CHOC</t>
+  </si>
+  <si>
+    <t>20052495</t>
+  </si>
+  <si>
+    <t>SARI/R SAND SRIK MDN</t>
+  </si>
+  <si>
+    <t>20062099</t>
+  </si>
+  <si>
+    <t>S/ROTI DORAYAKI CKLT</t>
+  </si>
+  <si>
+    <t>20132618</t>
+  </si>
+  <si>
+    <t>S/ROTI ZPR SNDW MCHA</t>
+  </si>
+  <si>
+    <t>20046106</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND K/KJU</t>
+  </si>
+  <si>
+    <t>20130214</t>
+  </si>
+  <si>
+    <t>S/ROTI DRYKI CHSE.HK</t>
+  </si>
+  <si>
+    <t>20132619</t>
+  </si>
+  <si>
+    <t>S/ROTI ZPR SNDW CRMY</t>
+  </si>
+  <si>
+    <t>20035999</t>
+  </si>
+  <si>
+    <t>SARI ROTI SAND CKLT</t>
+  </si>
+  <si>
+    <t>20130215</t>
+  </si>
+  <si>
+    <t>S/ROTI DRYKI CHO.PNT</t>
+  </si>
+  <si>
+    <t>20134379</t>
+  </si>
+  <si>
+    <t>SARI/RT SAND CHO.BLS</t>
+  </si>
+  <si>
+    <t>20132621</t>
+  </si>
+  <si>
+    <t>S/ROTI SOFT PUTU PDN</t>
+  </si>
+  <si>
+    <t>20138652</t>
+  </si>
+  <si>
+    <t>SARI CAKE DORAYKI PS</t>
+  </si>
+  <si>
+    <t>20141863</t>
+  </si>
+  <si>
+    <t>SR SNDW GNDUM KEJU46</t>
+  </si>
+  <si>
+    <t>20091744</t>
+  </si>
+  <si>
+    <t>SR STMD CHEESE CAKE</t>
+  </si>
+  <si>
+    <t>20133258</t>
+  </si>
+  <si>
+    <t>S/ROTI DRYKI STRWBRY</t>
+  </si>
+  <si>
+    <t>20140128</t>
+  </si>
+  <si>
+    <t>SR.KUE CHS CAKE DUO</t>
+  </si>
+  <si>
+    <t>20135250</t>
+  </si>
+  <si>
+    <t>S/ROTI CHS CK STRWBR</t>
+  </si>
+  <si>
+    <t>20138651</t>
+  </si>
+  <si>
+    <t>SARI KUE WAFFLE ORG</t>
+  </si>
+  <si>
+    <t>20141958</t>
+  </si>
+  <si>
+    <t>SR BUN GANDUM CHES53</t>
+  </si>
+  <si>
+    <t>20099290</t>
+  </si>
+  <si>
+    <t>ARNON CHOCO ROLL</t>
+  </si>
+  <si>
+    <t>20054693</t>
+  </si>
+  <si>
+    <t>ARNON ROTI SSR MNTGA</t>
+  </si>
+  <si>
+    <t>20132973</t>
+  </si>
+  <si>
+    <t>ARNON ROTI SSR KEJU</t>
+  </si>
+  <si>
+    <t>20054691</t>
+  </si>
+  <si>
+    <t>ARNON ROTI MESES 5'S</t>
+  </si>
+  <si>
+    <t>20057573</t>
+  </si>
+  <si>
+    <t>ARNON RTI CRM MSS 40</t>
+  </si>
+  <si>
+    <t>20132974</t>
+  </si>
+  <si>
+    <t>ARNON STEAM CHS CAKE</t>
+  </si>
+  <si>
+    <t>20067468</t>
+  </si>
+  <si>
+    <t>ARNON ROTI PSNG CKLT</t>
+  </si>
+  <si>
+    <t>20137768</t>
+  </si>
+  <si>
+    <t>ARNON STEAM CAKE BAN</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>20127597</t>
+  </si>
+  <si>
+    <t>MR.BRD SNDW MRGRN</t>
+  </si>
+  <si>
+    <t>20134627</t>
+  </si>
+  <si>
+    <t>MR.BRD RT ISI DG AYM</t>
+  </si>
+  <si>
+    <t>20138653</t>
+  </si>
+  <si>
+    <t>MR.BREAD MUNG BEAN</t>
+  </si>
+  <si>
+    <t>20136705</t>
+  </si>
+  <si>
+    <t>MR.BREAD SOFT CHOCO</t>
+  </si>
+  <si>
+    <t>20127047</t>
+  </si>
+  <si>
+    <t>MR.BRD SBK SOFT CHSE</t>
+  </si>
+  <si>
+    <t>20129486</t>
+  </si>
+  <si>
+    <t>MR.BRD ISI KEJU SUSU</t>
+  </si>
+  <si>
+    <t>20137419</t>
+  </si>
+  <si>
+    <t>MR.BREAD CKLT KCNG</t>
+  </si>
+  <si>
+    <t>20069665</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR CKLT KEJU</t>
+  </si>
+  <si>
+    <t>20070168</t>
+  </si>
+  <si>
+    <t>MR.BREAD KSR CKLT SS</t>
+  </si>
+  <si>
+    <t>20104117</t>
+  </si>
+  <si>
+    <t>MR.BRD SISIR COKELAT</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20096536</t>
+  </si>
+  <si>
+    <t>MR.BRD SISIR MRGARIN</t>
+  </si>
+  <si>
+    <t>20064211</t>
+  </si>
+  <si>
+    <t>M/B  SANDW.CKLT SPCL</t>
+  </si>
+  <si>
+    <t>20087513</t>
+  </si>
+  <si>
+    <t>MR.BRD  SANDW KR.KJU</t>
+  </si>
+  <si>
+    <t>20139188</t>
+  </si>
+  <si>
+    <t>MR.BREAD SOFT SRKAYA</t>
+  </si>
+  <si>
+    <t>20135659</t>
+  </si>
+  <si>
+    <t>MR.BRD TAWAR TEBAL4S</t>
+  </si>
+  <si>
+    <t>20010387</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR KOMBINASI</t>
+  </si>
+  <si>
+    <t>20015478</t>
+  </si>
+  <si>
+    <t>MR.BREAD KASUR CKLT</t>
+  </si>
+  <si>
+    <t>10033661</t>
+  </si>
+  <si>
+    <t>MR.BREAD KASUR</t>
+  </si>
+  <si>
+    <t>10029545</t>
+  </si>
+  <si>
+    <t>MR.BREAD RT.SBK KEJU</t>
+  </si>
+  <si>
+    <t>20074955</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR CHO BNANA</t>
+  </si>
+  <si>
+    <t>20041084</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR PD COK SR</t>
+  </si>
+  <si>
+    <t>20140129</t>
+  </si>
+  <si>
+    <t>MR.BREAD CRM MEISES</t>
+  </si>
+  <si>
+    <t>20117083</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR TEBAL</t>
+  </si>
+  <si>
+    <t>20135734</t>
+  </si>
+  <si>
+    <t>MR.BRD TWR KUPAS 15S</t>
+  </si>
+  <si>
+    <t>20042205</t>
+  </si>
+  <si>
+    <t>MR.BRD TWR GANDUM MS</t>
+  </si>
+  <si>
+    <t>10031694</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR KUPAS</t>
+  </si>
+  <si>
+    <t>10029536</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR</t>
+  </si>
+  <si>
+    <t>20001203</t>
+  </si>
+  <si>
+    <t>MR.BREAD TW.KPS PAND</t>
+  </si>
+  <si>
+    <t>20020008</t>
+  </si>
+  <si>
+    <t>MR.BREAD MANIS CHO 4</t>
+  </si>
+  <si>
+    <t>20138580</t>
+  </si>
+  <si>
+    <t>PRM BREAD COOKIES</t>
   </si>
   <si>
     <t>14</t>
-  </si>
-  <si>
-    <t>20137857</t>
-  </si>
-  <si>
-    <t>SARI KUE PND.C 6S</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20036000</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND K/KCG</t>
-  </si>
-  <si>
-    <t>20072596</t>
-  </si>
-  <si>
-    <t>SARI ROTI LAPIS BMKH</t>
-  </si>
-  <si>
-    <t>20127599</t>
-  </si>
-  <si>
-    <t>S/R LPIS SRBY ORI 48</t>
-  </si>
-  <si>
-    <t>20046107</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND BLUBR</t>
-  </si>
-  <si>
-    <t>20080782</t>
-  </si>
-  <si>
-    <t>SR LAPIS BMKHN CKLAT</t>
-  </si>
-  <si>
-    <t>20132616</t>
-  </si>
-  <si>
-    <t>S/ROTI ZPR SNDW CHOC</t>
-  </si>
-  <si>
-    <t>20052495</t>
-  </si>
-  <si>
-    <t>SARI/R SAND SRIK MDN</t>
-  </si>
-  <si>
-    <t>20062099</t>
-  </si>
-  <si>
-    <t>S/ROTI DORAYAKI CKLT</t>
-  </si>
-  <si>
-    <t>20132618</t>
-  </si>
-  <si>
-    <t>S/ROTI ZPR SNDW MCHA</t>
-  </si>
-  <si>
-    <t>20046106</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND K/KJU</t>
-  </si>
-  <si>
-    <t>20130214</t>
-  </si>
-  <si>
-    <t>S/ROTI DRYKI CHSE.HK</t>
-  </si>
-  <si>
-    <t>20132619</t>
-  </si>
-  <si>
-    <t>S/ROTI ZPR SNDW CRMY</t>
-  </si>
-  <si>
-    <t>20035999</t>
-  </si>
-  <si>
-    <t>SARI ROTI SAND CKLT</t>
-  </si>
-  <si>
-    <t>20130215</t>
-  </si>
-  <si>
-    <t>S/ROTI DRYKI CHO.PNT</t>
-  </si>
-  <si>
-    <t>20134379</t>
-  </si>
-  <si>
-    <t>SARI/RT SAND CHO.BLS</t>
-  </si>
-  <si>
-    <t>20132621</t>
-  </si>
-  <si>
-    <t>S/ROTI SOFT PUTU PDN</t>
-  </si>
-  <si>
-    <t>20138652</t>
-  </si>
-  <si>
-    <t>SARI CAKE DORAYKI PS</t>
-  </si>
-  <si>
-    <t>20141863</t>
-  </si>
-  <si>
-    <t>SR SNDW GNDUM KEJU46</t>
-  </si>
-  <si>
-    <t>20091744</t>
-  </si>
-  <si>
-    <t>SR STMD CHEESE CAKE</t>
-  </si>
-  <si>
-    <t>20133258</t>
-  </si>
-  <si>
-    <t>S/ROTI DRYKI STRWBRY</t>
-  </si>
-  <si>
-    <t>20140128</t>
-  </si>
-  <si>
-    <t>SR.KUE CHS CAKE DUO</t>
-  </si>
-  <si>
-    <t>20135250</t>
-  </si>
-  <si>
-    <t>S/ROTI CHS CK STRWBR</t>
-  </si>
-  <si>
-    <t>20138651</t>
-  </si>
-  <si>
-    <t>SARI KUE WAFFLE ORG</t>
-  </si>
-  <si>
-    <t>20141958</t>
-  </si>
-  <si>
-    <t>SR BUN GANDUM CHES53</t>
-  </si>
-  <si>
-    <t>20142425</t>
-  </si>
-  <si>
-    <t>S/R WAFFLE CHOCO 35G</t>
-  </si>
-  <si>
-    <t>20099290</t>
-  </si>
-  <si>
-    <t>ARNON CHOCO ROLL</t>
-  </si>
-  <si>
-    <t>20054693</t>
-  </si>
-  <si>
-    <t>ARNON ROTI SSR MNTGA</t>
-  </si>
-  <si>
-    <t>20132973</t>
-  </si>
-  <si>
-    <t>ARNON ROTI SSR KEJU</t>
-  </si>
-  <si>
-    <t>20054691</t>
-  </si>
-  <si>
-    <t>ARNON ROTI MESES 5'S</t>
-  </si>
-  <si>
-    <t>20057573</t>
-  </si>
-  <si>
-    <t>ARNON RTI CRM MSS 40</t>
-  </si>
-  <si>
-    <t>20132974</t>
-  </si>
-  <si>
-    <t>ARNON STEAM CHS CAKE</t>
-  </si>
-  <si>
-    <t>20067468</t>
-  </si>
-  <si>
-    <t>ARNON ROTI PSNG CKLT</t>
-  </si>
-  <si>
-    <t>20137768</t>
-  </si>
-  <si>
-    <t>ARNON STEAM CAKE BAN</t>
-  </si>
-  <si>
-    <t>10029542</t>
-  </si>
-  <si>
-    <t>MR.BREAD COKLAT KEJU</t>
-  </si>
-  <si>
-    <t>20127597</t>
-  </si>
-  <si>
-    <t>MR.BRD SNDW MRGRN</t>
-  </si>
-  <si>
-    <t>20134627</t>
-  </si>
-  <si>
-    <t>MR.BRD RT ISI DG AYM</t>
-  </si>
-  <si>
-    <t>20138653</t>
-  </si>
-  <si>
-    <t>MR.BREAD MUNG BEAN</t>
-  </si>
-  <si>
-    <t>20136705</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT CHOCO</t>
-  </si>
-  <si>
-    <t>20127047</t>
-  </si>
-  <si>
-    <t>MR.BRD SBK SOFT CHSE</t>
-  </si>
-  <si>
-    <t>20129486</t>
-  </si>
-  <si>
-    <t>MR.BRD ISI KEJU SUSU</t>
-  </si>
-  <si>
-    <t>20137419</t>
-  </si>
-  <si>
-    <t>MR.BREAD CKLT KCNG</t>
-  </si>
-  <si>
-    <t>20069665</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR CKLT KEJU</t>
-  </si>
-  <si>
-    <t>20070168</t>
-  </si>
-  <si>
-    <t>MR.BREAD KSR CKLT SS</t>
-  </si>
-  <si>
-    <t>20104117</t>
-  </si>
-  <si>
-    <t>MR.BRD SISIR COKELAT</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20096536</t>
-  </si>
-  <si>
-    <t>MR.BRD SISIR MRGARIN</t>
-  </si>
-  <si>
-    <t>20064211</t>
-  </si>
-  <si>
-    <t>M/B  SANDW.CKLT SPCL</t>
-  </si>
-  <si>
-    <t>20087513</t>
-  </si>
-  <si>
-    <t>MR.BRD  SANDW KR.KJU</t>
-  </si>
-  <si>
-    <t>20139188</t>
-  </si>
-  <si>
-    <t>MR.BREAD SOFT SRKAYA</t>
-  </si>
-  <si>
-    <t>20135659</t>
-  </si>
-  <si>
-    <t>MR.BRD TAWAR TEBAL4S</t>
-  </si>
-  <si>
-    <t>20010387</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR KOMBINASI</t>
-  </si>
-  <si>
-    <t>20015478</t>
-  </si>
-  <si>
-    <t>MR.BREAD KASUR CKLT</t>
-  </si>
-  <si>
-    <t>10033661</t>
-  </si>
-  <si>
-    <t>MR.BREAD KASUR</t>
-  </si>
-  <si>
-    <t>10029545</t>
-  </si>
-  <si>
-    <t>MR.BREAD RT.SBK KEJU</t>
-  </si>
-  <si>
-    <t>20074955</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR CHO BNANA</t>
-  </si>
-  <si>
-    <t>20041084</t>
-  </si>
-  <si>
-    <t>MR.BRD KSR PD COK SR</t>
-  </si>
-  <si>
-    <t>20140129</t>
-  </si>
-  <si>
-    <t>MR.BREAD CRM MEISES</t>
-  </si>
-  <si>
-    <t>20117083</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR TEBAL</t>
-  </si>
-  <si>
-    <t>20135734</t>
-  </si>
-  <si>
-    <t>MR.BRD TWR KUPAS 15S</t>
-  </si>
-  <si>
-    <t>20042205</t>
-  </si>
-  <si>
-    <t>MR.BRD TWR GANDUM MS</t>
-  </si>
-  <si>
-    <t>10031694</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR KUPAS</t>
-  </si>
-  <si>
-    <t>10029536</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR</t>
-  </si>
-  <si>
-    <t>20001203</t>
-  </si>
-  <si>
-    <t>MR.BREAD TW.KPS PAND</t>
-  </si>
-  <si>
-    <t>20020008</t>
-  </si>
-  <si>
-    <t>MR.BREAD MANIS CHO 4</t>
-  </si>
-  <si>
-    <t>20138580</t>
-  </si>
-  <si>
-    <t>PRM BREAD COOKIES</t>
   </si>
   <si>
     <t>20125697</t>
@@ -1273,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2375,10 +2354,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2386,19 +2365,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2406,10 +2385,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2426,10 +2405,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2438,7 +2417,7 @@
         <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2446,10 +2425,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2458,7 +2437,7 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2466,10 +2445,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2486,10 +2465,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2498,7 +2477,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2506,10 +2485,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2518,7 +2497,7 @@
         <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2526,10 +2505,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2546,10 +2525,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2558,7 +2537,7 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2566,10 +2545,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2578,7 +2557,7 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2586,10 +2565,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2606,10 +2585,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2618,7 +2597,7 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2626,10 +2605,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2638,7 +2617,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2646,10 +2625,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2666,10 +2645,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2678,7 +2657,7 @@
         <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2686,10 +2665,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2698,7 +2677,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2706,10 +2685,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2726,10 +2705,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2738,7 +2717,7 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2746,10 +2725,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2758,7 +2737,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2766,10 +2745,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2786,10 +2765,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2798,7 +2777,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2806,10 +2785,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2818,7 +2797,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2826,10 +2805,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2846,19 +2825,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2866,19 +2845,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2886,19 +2865,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2906,10 +2885,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2918,7 +2897,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2926,19 +2905,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2946,19 +2925,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2966,19 +2945,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2986,10 +2965,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -2998,7 +2977,7 @@
         <v>42</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3006,19 +2985,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3026,19 +3005,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3046,19 +3025,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3066,10 +3045,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3078,7 +3057,7 @@
         <v>46</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3086,10 +3065,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3098,7 +3077,7 @@
         <v>46</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3106,10 +3085,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3118,7 +3097,7 @@
         <v>46</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3126,10 +3105,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3138,7 +3117,7 @@
         <v>46</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3146,10 +3125,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3158,7 +3137,7 @@
         <v>46</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3166,19 +3145,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3186,19 +3165,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3206,30 +3185,30 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3238,7 +3217,7 @@
         <v>49</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3246,10 +3225,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3258,7 +3237,7 @@
         <v>49</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3266,10 +3245,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3278,18 +3257,18 @@
         <v>49</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>218</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3298,7 +3277,7 @@
         <v>49</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3306,19 +3285,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3326,19 +3305,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3346,19 +3325,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3366,10 +3345,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3378,7 +3357,7 @@
         <v>52</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3386,10 +3365,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3398,7 +3377,7 @@
         <v>52</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3406,10 +3385,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3418,7 +3397,7 @@
         <v>52</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3426,10 +3405,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3438,7 +3417,7 @@
         <v>52</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3446,10 +3425,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3458,7 +3437,7 @@
         <v>52</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3466,19 +3445,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3486,19 +3465,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3506,19 +3485,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3526,10 +3505,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3538,7 +3517,7 @@
         <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3546,10 +3525,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3558,7 +3537,7 @@
         <v>123</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3566,10 +3545,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3578,7 +3557,7 @@
         <v>123</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3586,10 +3565,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3598,7 +3577,7 @@
         <v>123</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3606,19 +3585,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3626,19 +3605,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>123</v>
+        <v>251</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3646,19 +3625,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>123</v>
+        <v>251</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3666,19 +3645,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3686,19 +3665,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3706,19 +3685,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3726,19 +3705,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3746,19 +3725,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>46</v>
+        <v>251</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3766,19 +3745,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3795,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>123</v>
+        <v>271</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3806,62 +3785,62 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>126</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>275</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>126</v>
+        <v>274</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>278</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3875,93 +3854,33 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
